--- a/data/nzd0258/nzd0258.xlsx
+++ b/data/nzd0258/nzd0258.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O359"/>
+  <dimension ref="A1:O360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18723,6 +18723,57 @@
         <v>368.97</v>
       </c>
       <c r="O359" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>351.57</v>
+      </c>
+      <c r="C360" t="n">
+        <v>355.08</v>
+      </c>
+      <c r="D360" t="n">
+        <v>356.67</v>
+      </c>
+      <c r="E360" t="n">
+        <v>358.64</v>
+      </c>
+      <c r="F360" t="n">
+        <v>353.33</v>
+      </c>
+      <c r="G360" t="n">
+        <v>352.91</v>
+      </c>
+      <c r="H360" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="I360" t="n">
+        <v>362.18</v>
+      </c>
+      <c r="J360" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="K360" t="n">
+        <v>357.2</v>
+      </c>
+      <c r="L360" t="n">
+        <v>367.74</v>
+      </c>
+      <c r="M360" t="n">
+        <v>365.37</v>
+      </c>
+      <c r="N360" t="n">
+        <v>373.44</v>
+      </c>
+      <c r="O360" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -18739,7 +18790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B376"/>
+  <dimension ref="A1:B377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22502,6 +22553,16 @@
       </c>
       <c r="B376" t="n">
         <v>1.64</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>-0.77</v>
       </c>
     </row>
   </sheetData>
@@ -22670,28 +22731,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>1.213428243928675</v>
+        <v>1.214997003634312</v>
       </c>
       <c r="J2" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K2" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3032066829379947</v>
+        <v>0.304911200770118</v>
       </c>
       <c r="M2" t="n">
-        <v>11.15076245822738</v>
+        <v>11.12718063790746</v>
       </c>
       <c r="N2" t="n">
-        <v>189.3026427837574</v>
+        <v>188.7969633196528</v>
       </c>
       <c r="O2" t="n">
-        <v>13.75872969368021</v>
+        <v>13.74034072793149</v>
       </c>
       <c r="P2" t="n">
-        <v>316.3567598077949</v>
+        <v>316.3399829201128</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22748,28 +22809,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9834456645337599</v>
+        <v>0.9901117911390114</v>
       </c>
       <c r="J3" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K3" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2751106561387147</v>
+        <v>0.2783119658418367</v>
       </c>
       <c r="M3" t="n">
-        <v>9.880615522397305</v>
+        <v>9.892530517352515</v>
       </c>
       <c r="N3" t="n">
-        <v>142.5700539050245</v>
+        <v>142.6145282016298</v>
       </c>
       <c r="O3" t="n">
-        <v>11.94027026097083</v>
+        <v>11.9421324813297</v>
       </c>
       <c r="P3" t="n">
-        <v>316.3111056538871</v>
+        <v>316.2398156679645</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22826,28 +22887,28 @@
         <v>0.0755</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8506053135237976</v>
+        <v>0.8610339513792272</v>
       </c>
       <c r="J4" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K4" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1288871431565215</v>
+        <v>0.1318344628406388</v>
       </c>
       <c r="M4" t="n">
-        <v>13.55726176902869</v>
+        <v>13.57294271422671</v>
       </c>
       <c r="N4" t="n">
-        <v>273.5799586205767</v>
+        <v>273.8998659691137</v>
       </c>
       <c r="O4" t="n">
-        <v>16.54025267704749</v>
+        <v>16.54992042183628</v>
       </c>
       <c r="P4" t="n">
-        <v>314.292922551474</v>
+        <v>314.1813948998209</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22904,28 +22965,28 @@
         <v>0.0588</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3835656869277045</v>
+        <v>0.3929863059900638</v>
       </c>
       <c r="J5" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K5" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04754807375787407</v>
+        <v>0.04980527210182761</v>
       </c>
       <c r="M5" t="n">
-        <v>10.26167321856468</v>
+        <v>10.28300004584736</v>
       </c>
       <c r="N5" t="n">
-        <v>164.8742775739194</v>
+        <v>165.2988425429614</v>
       </c>
       <c r="O5" t="n">
-        <v>12.84033790731067</v>
+        <v>12.85685974656959</v>
       </c>
       <c r="P5" t="n">
-        <v>330.5839207669014</v>
+        <v>330.4831732353725</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22982,28 +23043,28 @@
         <v>0.0959</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6106041764530546</v>
+        <v>0.6148824983922757</v>
       </c>
       <c r="J6" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K6" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1491977924300523</v>
+        <v>0.1515009958973378</v>
       </c>
       <c r="M6" t="n">
-        <v>8.646607494298951</v>
+        <v>8.647086919135093</v>
       </c>
       <c r="N6" t="n">
-        <v>119.2859407181246</v>
+        <v>119.1350358092469</v>
       </c>
       <c r="O6" t="n">
-        <v>10.92181032238358</v>
+        <v>10.91489971595007</v>
       </c>
       <c r="P6" t="n">
-        <v>328.9855013035721</v>
+        <v>328.9398513090022</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23060,28 +23121,28 @@
         <v>0.0877</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5541325231238206</v>
+        <v>0.5568263110930654</v>
       </c>
       <c r="J7" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K7" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1574005708105743</v>
+        <v>0.1593369342084912</v>
       </c>
       <c r="M7" t="n">
-        <v>7.523228868693518</v>
+        <v>7.517872957081448</v>
       </c>
       <c r="N7" t="n">
-        <v>91.77661382320058</v>
+        <v>91.59310331599617</v>
       </c>
       <c r="O7" t="n">
-        <v>9.580011159868269</v>
+        <v>9.570428585805141</v>
       </c>
       <c r="P7" t="n">
-        <v>333.0803281252511</v>
+        <v>333.0515367066118</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23138,28 +23199,28 @@
         <v>0.0696</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4357172253789659</v>
+        <v>0.4418500926993129</v>
       </c>
       <c r="J8" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K8" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07507865480427156</v>
+        <v>0.0772388089069953</v>
       </c>
       <c r="M8" t="n">
-        <v>9.130864888509546</v>
+        <v>9.134664457032201</v>
       </c>
       <c r="N8" t="n">
-        <v>130.5833090473405</v>
+        <v>130.5934576178735</v>
       </c>
       <c r="O8" t="n">
-        <v>11.42730541498478</v>
+        <v>11.42774945550844</v>
       </c>
       <c r="P8" t="n">
-        <v>332.9679710992627</v>
+        <v>332.9024225288128</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23216,28 +23277,28 @@
         <v>0.0615</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5130388107420474</v>
+        <v>0.5214371882571343</v>
       </c>
       <c r="J9" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K9" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L9" t="n">
-        <v>0.112678377058771</v>
+        <v>0.1159211700740692</v>
       </c>
       <c r="M9" t="n">
-        <v>8.320037541050365</v>
+        <v>8.341117714971237</v>
       </c>
       <c r="N9" t="n">
-        <v>115.7259657051568</v>
+        <v>116.1047544081523</v>
       </c>
       <c r="O9" t="n">
-        <v>10.7576003692811</v>
+        <v>10.77519161816403</v>
       </c>
       <c r="P9" t="n">
-        <v>332.6130163476088</v>
+        <v>332.5232538252097</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23294,28 +23355,28 @@
         <v>0.0983</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3392884694718755</v>
+        <v>0.3468853973848692</v>
       </c>
       <c r="J10" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K10" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05280317867481543</v>
+        <v>0.05509468996137135</v>
       </c>
       <c r="M10" t="n">
-        <v>8.469215848443675</v>
+        <v>8.485956689887809</v>
       </c>
       <c r="N10" t="n">
-        <v>115.8568920519551</v>
+        <v>116.1100919806966</v>
       </c>
       <c r="O10" t="n">
-        <v>10.76368394426161</v>
+        <v>10.77543929409361</v>
       </c>
       <c r="P10" t="n">
-        <v>334.062423918019</v>
+        <v>333.9813641654097</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23372,28 +23433,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2925937082410559</v>
+        <v>0.300990837998158</v>
       </c>
       <c r="J11" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K11" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03023270298325176</v>
+        <v>0.03196826603077019</v>
       </c>
       <c r="M11" t="n">
-        <v>9.855756210967231</v>
+        <v>9.870822268681238</v>
       </c>
       <c r="N11" t="n">
-        <v>154.0721103859225</v>
+        <v>154.346381776272</v>
       </c>
       <c r="O11" t="n">
-        <v>12.41257871620247</v>
+        <v>12.42362192664732</v>
       </c>
       <c r="P11" t="n">
-        <v>333.4824952158269</v>
+        <v>333.3928972535276</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23450,28 +23511,28 @@
         <v>0.1039</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4101676118451918</v>
+        <v>0.4218371142423211</v>
       </c>
       <c r="J12" t="n">
+        <v>359</v>
+      </c>
+      <c r="K12" t="n">
         <v>358</v>
       </c>
-      <c r="K12" t="n">
-        <v>357</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.048149908573758</v>
+        <v>0.05070678903709092</v>
       </c>
       <c r="M12" t="n">
-        <v>10.86916315986779</v>
+        <v>10.90845314249806</v>
       </c>
       <c r="N12" t="n">
-        <v>185.4628513462325</v>
+        <v>186.2977945992656</v>
       </c>
       <c r="O12" t="n">
-        <v>13.61847463360829</v>
+        <v>13.6490950102659</v>
       </c>
       <c r="P12" t="n">
-        <v>334.7447529338679</v>
+        <v>334.6198062684111</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23528,28 +23589,28 @@
         <v>0.0806</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4316870375783362</v>
+        <v>0.4401283361072049</v>
       </c>
       <c r="J13" t="n">
+        <v>359</v>
+      </c>
+      <c r="K13" t="n">
         <v>358</v>
       </c>
-      <c r="K13" t="n">
-        <v>357</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.03391537178194315</v>
+        <v>0.03531700883789346</v>
       </c>
       <c r="M13" t="n">
-        <v>13.04411083057427</v>
+        <v>13.06228008683563</v>
       </c>
       <c r="N13" t="n">
-        <v>296.0177280879828</v>
+        <v>295.8988255456503</v>
       </c>
       <c r="O13" t="n">
-        <v>17.20516573846305</v>
+        <v>17.20170995993277</v>
       </c>
       <c r="P13" t="n">
-        <v>337.9136769682016</v>
+        <v>337.8232950420994</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23606,28 +23667,28 @@
         <v>0.0444</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7840701818590821</v>
+        <v>0.7939350772678403</v>
       </c>
       <c r="J14" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K14" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1016438914915945</v>
+        <v>0.1041758297155863</v>
       </c>
       <c r="M14" t="n">
-        <v>12.64832835559405</v>
+        <v>12.66353132374711</v>
       </c>
       <c r="N14" t="n">
-        <v>305.7919916379635</v>
+        <v>305.9084890784404</v>
       </c>
       <c r="O14" t="n">
-        <v>17.48690915050351</v>
+        <v>17.49023982335406</v>
       </c>
       <c r="P14" t="n">
-        <v>333.8950024297167</v>
+        <v>333.7899592220951</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23665,7 +23726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O359"/>
+  <dimension ref="A1:O360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51235,6 +51296,83 @@
         </is>
       </c>
     </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>-38.42609933073391,174.6413476506231</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>-38.42540910544938,174.64117026875516</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>-38.424716024772856,174.64101457788402</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-38.424023501147026,174.64085459452278</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>-38.423320169951076,174.64077685227736</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>-38.42262408707502,174.64064386807743</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-38.42193344714869,174.64046921741917</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>-38.421248791908326,174.64025565295208</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>-38.42054852880625,174.64014928938775</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>-38.4198553412638,174.63999354110592</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>-38.419180547172914,174.63971587078566</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>-38.41848383260053,174.63958340544502</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>-38.4178048322418,174.63933351873467</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0258/nzd0258.xlsx
+++ b/data/nzd0258/nzd0258.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O360"/>
+  <dimension ref="A1:O361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18669,7 +18669,7 @@
         <v>354.18</v>
       </c>
       <c r="N358" t="n">
-        <v>362.26</v>
+        <v>327.76</v>
       </c>
       <c r="O358" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>360.87</v>
       </c>
       <c r="N359" t="n">
-        <v>368.97</v>
+        <v>319.33</v>
       </c>
       <c r="O359" t="inlineStr">
         <is>
@@ -18771,9 +18771,60 @@
         <v>365.37</v>
       </c>
       <c r="N360" t="n">
-        <v>373.44</v>
+        <v>310.27</v>
       </c>
       <c r="O360" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>351.57</v>
+      </c>
+      <c r="C361" t="n">
+        <v>355.08</v>
+      </c>
+      <c r="D361" t="n">
+        <v>356.67</v>
+      </c>
+      <c r="E361" t="n">
+        <v>358.64</v>
+      </c>
+      <c r="F361" t="n">
+        <v>353.33</v>
+      </c>
+      <c r="G361" t="n">
+        <v>352.91</v>
+      </c>
+      <c r="H361" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="I361" t="n">
+        <v>362.18</v>
+      </c>
+      <c r="J361" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="K361" t="n">
+        <v>359.36</v>
+      </c>
+      <c r="L361" t="n">
+        <v>371.1</v>
+      </c>
+      <c r="M361" t="n">
+        <v>366.52</v>
+      </c>
+      <c r="N361" t="n">
+        <v>310.27</v>
+      </c>
+      <c r="O361" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -18790,7 +18841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B377"/>
+  <dimension ref="A1:B378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22563,6 +22614,16 @@
       </c>
       <c r="B377" t="n">
         <v>-0.77</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>-0.84</v>
       </c>
     </row>
   </sheetData>
@@ -22731,28 +22792,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>1.214997003634312</v>
+        <v>1.216518094818145</v>
       </c>
       <c r="J2" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K2" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L2" t="n">
-        <v>0.304911200770118</v>
+        <v>0.3066016824493327</v>
       </c>
       <c r="M2" t="n">
-        <v>11.12718063790746</v>
+        <v>11.10346529953006</v>
       </c>
       <c r="N2" t="n">
-        <v>188.7969633196528</v>
+        <v>188.2928388663802</v>
       </c>
       <c r="O2" t="n">
-        <v>13.74034072793149</v>
+        <v>13.72198378028411</v>
       </c>
       <c r="P2" t="n">
-        <v>316.3399829201128</v>
+        <v>316.3236824465044</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22809,28 +22870,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9901117911390114</v>
+        <v>0.9966713480590922</v>
       </c>
       <c r="J3" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K3" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2783119658418367</v>
+        <v>0.2814878388342357</v>
       </c>
       <c r="M3" t="n">
-        <v>9.892530517352515</v>
+        <v>9.903674687179695</v>
       </c>
       <c r="N3" t="n">
-        <v>142.6145282016298</v>
+        <v>142.6483789236955</v>
       </c>
       <c r="O3" t="n">
-        <v>11.9421324813297</v>
+        <v>11.94354967853759</v>
       </c>
       <c r="P3" t="n">
-        <v>316.2398156679645</v>
+        <v>316.1695214702235</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22887,28 +22948,28 @@
         <v>0.0755</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8610339513792272</v>
+        <v>0.8713116937264772</v>
       </c>
       <c r="J4" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K4" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1318344628406388</v>
+        <v>0.1347734749397634</v>
       </c>
       <c r="M4" t="n">
-        <v>13.57294271422671</v>
+        <v>13.58790186819441</v>
       </c>
       <c r="N4" t="n">
-        <v>273.8998659691137</v>
+        <v>274.1958588215637</v>
       </c>
       <c r="O4" t="n">
-        <v>16.54992042183628</v>
+        <v>16.5588604324562</v>
       </c>
       <c r="P4" t="n">
-        <v>314.1813948998209</v>
+        <v>314.0712555014299</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22965,28 +23026,28 @@
         <v>0.0588</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3929863059900638</v>
+        <v>0.4022794671165517</v>
       </c>
       <c r="J5" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K5" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04980527210182761</v>
+        <v>0.05208115994846507</v>
       </c>
       <c r="M5" t="n">
-        <v>10.28300004584736</v>
+        <v>10.30449226052488</v>
       </c>
       <c r="N5" t="n">
-        <v>165.2988425429614</v>
+        <v>165.7046311176895</v>
       </c>
       <c r="O5" t="n">
-        <v>12.85685974656959</v>
+        <v>12.87263108760946</v>
       </c>
       <c r="P5" t="n">
-        <v>330.4831732353725</v>
+        <v>330.3835849074072</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23043,28 +23104,28 @@
         <v>0.0959</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6148824983922757</v>
+        <v>0.6190928548551614</v>
       </c>
       <c r="J6" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K6" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1515009958973378</v>
+        <v>0.1537949581698836</v>
       </c>
       <c r="M6" t="n">
-        <v>8.647086919135093</v>
+        <v>8.647734154651411</v>
       </c>
       <c r="N6" t="n">
-        <v>119.1350358092469</v>
+        <v>118.9807309911325</v>
       </c>
       <c r="O6" t="n">
-        <v>10.91489971595007</v>
+        <v>10.90782888530676</v>
       </c>
       <c r="P6" t="n">
-        <v>328.9398513090022</v>
+        <v>328.8948341969121</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23121,28 +23182,28 @@
         <v>0.0877</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5568263110930654</v>
+        <v>0.5594734014319542</v>
       </c>
       <c r="J7" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K7" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1593369342084912</v>
+        <v>0.1612642875281723</v>
       </c>
       <c r="M7" t="n">
-        <v>7.517872957081448</v>
+        <v>7.512216006736839</v>
       </c>
       <c r="N7" t="n">
-        <v>91.59310331599617</v>
+        <v>91.40873542388091</v>
       </c>
       <c r="O7" t="n">
-        <v>9.570428585805141</v>
+        <v>9.560791568896422</v>
       </c>
       <c r="P7" t="n">
-        <v>333.0515367066118</v>
+        <v>333.023186803905</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23199,28 +23260,28 @@
         <v>0.0696</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4418500926993129</v>
+        <v>0.4478956341015423</v>
       </c>
       <c r="J8" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K8" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0772388089069953</v>
+        <v>0.07940265152850845</v>
       </c>
       <c r="M8" t="n">
-        <v>9.134664457032201</v>
+        <v>9.137896282688985</v>
       </c>
       <c r="N8" t="n">
-        <v>130.5934576178735</v>
+        <v>130.5961134226648</v>
       </c>
       <c r="O8" t="n">
-        <v>11.42774945550844</v>
+        <v>11.42786565473469</v>
       </c>
       <c r="P8" t="n">
-        <v>332.9024225288128</v>
+        <v>332.8376757734623</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23277,28 +23338,28 @@
         <v>0.0615</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5214371882571343</v>
+        <v>0.5297179042731719</v>
       </c>
       <c r="J9" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K9" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1159211700740692</v>
+        <v>0.1191580185657205</v>
       </c>
       <c r="M9" t="n">
-        <v>8.341117714971237</v>
+        <v>8.362053762146239</v>
       </c>
       <c r="N9" t="n">
-        <v>116.1047544081523</v>
+        <v>116.4678118877086</v>
       </c>
       <c r="O9" t="n">
-        <v>10.77519161816403</v>
+        <v>10.79202538394479</v>
       </c>
       <c r="P9" t="n">
-        <v>332.5232538252097</v>
+        <v>332.4345687169049</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23355,28 +23416,28 @@
         <v>0.0983</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3468853973848692</v>
+        <v>0.3543787572770684</v>
       </c>
       <c r="J10" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K10" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05509468996137135</v>
+        <v>0.05740149860807675</v>
       </c>
       <c r="M10" t="n">
-        <v>8.485956689887809</v>
+        <v>8.502214745292623</v>
       </c>
       <c r="N10" t="n">
-        <v>116.1100919806966</v>
+        <v>116.3510789198381</v>
       </c>
       <c r="O10" t="n">
-        <v>10.77543929409361</v>
+        <v>10.78661573060977</v>
       </c>
       <c r="P10" t="n">
-        <v>333.9813641654097</v>
+        <v>333.9012451956332</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23433,28 +23494,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.300990837998158</v>
+        <v>0.3104092070976993</v>
       </c>
       <c r="J11" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K11" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03196826603077019</v>
+        <v>0.03392480382249408</v>
       </c>
       <c r="M11" t="n">
-        <v>9.870822268681238</v>
+        <v>9.890761440765571</v>
       </c>
       <c r="N11" t="n">
-        <v>154.346381776272</v>
+        <v>154.8083261411377</v>
       </c>
       <c r="O11" t="n">
-        <v>12.42362192664732</v>
+        <v>12.44219940931416</v>
       </c>
       <c r="P11" t="n">
-        <v>333.3928972535276</v>
+        <v>333.2921960940897</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23511,28 +23572,28 @@
         <v>0.1039</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4218371142423211</v>
+        <v>0.4351171611006221</v>
       </c>
       <c r="J12" t="n">
+        <v>360</v>
+      </c>
+      <c r="K12" t="n">
         <v>359</v>
       </c>
-      <c r="K12" t="n">
-        <v>358</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.05070678903709092</v>
+        <v>0.05357999114036516</v>
       </c>
       <c r="M12" t="n">
-        <v>10.90845314249806</v>
+        <v>10.95699048184631</v>
       </c>
       <c r="N12" t="n">
-        <v>186.2977945992656</v>
+        <v>187.5411672479245</v>
       </c>
       <c r="O12" t="n">
-        <v>13.6490950102659</v>
+        <v>13.6945670704818</v>
       </c>
       <c r="P12" t="n">
-        <v>334.6198062684111</v>
+        <v>334.4773253818726</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23589,28 +23650,28 @@
         <v>0.0806</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4401283361072049</v>
+        <v>0.4490588077314983</v>
       </c>
       <c r="J13" t="n">
+        <v>360</v>
+      </c>
+      <c r="K13" t="n">
         <v>359</v>
       </c>
-      <c r="K13" t="n">
-        <v>358</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.03531700883789346</v>
+        <v>0.03681426987739145</v>
       </c>
       <c r="M13" t="n">
-        <v>13.06228008683563</v>
+        <v>13.08368907453634</v>
       </c>
       <c r="N13" t="n">
-        <v>295.8988255456503</v>
+        <v>295.8715454119081</v>
       </c>
       <c r="O13" t="n">
-        <v>17.20170995993277</v>
+        <v>17.20091699334393</v>
       </c>
       <c r="P13" t="n">
-        <v>337.8232950420994</v>
+        <v>337.7274805071198</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23667,28 +23728,28 @@
         <v>0.0444</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7939350772678403</v>
+        <v>0.6942989844593223</v>
       </c>
       <c r="J14" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K14" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1041758297155863</v>
+        <v>0.07873580714975137</v>
       </c>
       <c r="M14" t="n">
-        <v>12.66353132374711</v>
+        <v>12.93602629375448</v>
       </c>
       <c r="N14" t="n">
-        <v>305.9084890784404</v>
+        <v>319.2152685652172</v>
       </c>
       <c r="O14" t="n">
-        <v>17.49023982335406</v>
+        <v>17.86659644602791</v>
       </c>
       <c r="P14" t="n">
-        <v>333.7899592220951</v>
+        <v>334.8470916042741</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23726,7 +23787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O360"/>
+  <dimension ref="A1:O361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51210,7 +51271,7 @@
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t>-38.41778585535895,174.6394592625411</t>
+          <t>-38.41772729436857,174.63984729083737</t>
         </is>
       </c>
       <c r="O358" t="inlineStr">
@@ -51287,7 +51348,7 @@
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t>-38.41779724489948,174.63938379377126</t>
+          <t>-38.4177129849245,174.63994210460595</t>
         </is>
       </c>
       <c r="O359" t="inlineStr">
@@ -51364,10 +51425,87 @@
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t>-38.4178048322418,174.63933351873467</t>
+          <t>-38.41769760600672,174.6400440040563</t>
         </is>
       </c>
       <c r="O360" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>-38.42609933073391,174.6413476506231</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>-38.42540910544938,174.64117026875516</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>-38.424716024772856,174.64101457788402</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-38.424023501147026,174.64085459452278</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>-38.423320169951076,174.64077685227736</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-38.42262408707502,174.64064386807743</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-38.42193344714869,174.64046921741917</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-38.421248791908326,174.64025565295208</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>-38.42054852880625,174.64014928938775</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>-38.41985900773636,174.63996924647043</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>-38.41918625049527,174.63967807945875</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>-38.41848578462131,174.6395704710353</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>-38.41769760600672,174.6400440040563</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
